--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,697 +808,697 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9411,0.0089,0.0168,0.0022</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9330,0.0006,0.0003,0.0628</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0004,0.9991</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0002,0.0000</t>
+    <t>0.8825,0.0049,0.0564,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9426,0.0004,0.0015,0.0338</t>
+  </si>
+  <si>
+    <t>0.0285,0.0000,0.0004,0.9906</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5665,0.0004,0.5394,0.0001</t>
-  </si>
-  <si>
-    <t>0.3168,0.0011,0.7631,0.0002</t>
-  </si>
-  <si>
-    <t>0.1364,0.0002,0.9485,0.0000</t>
-  </si>
-  <si>
-    <t>0.0172,0.0001,0.9905,0.0001</t>
-  </si>
-  <si>
-    <t>0.9720,0.0001,0.0276,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
+    <t>0.9721,0.0013,0.0124,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.0015,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0371,0.0013,0.9764,0.0000</t>
+  </si>
+  <si>
+    <t>0.0072,0.0006,0.9942,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0002,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0072,0.9882,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9977,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8506,0.0005,0.0952,0.0034</t>
+  </si>
+  <si>
+    <t>0.2055,0.0006,0.7455,0.0019</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0587,0.0001,0.9761,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.0000,0.9918,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.1085,0.9008,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0766,0.1193,0.6857,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.9987,0.0009</t>
+  </si>
+  <si>
+    <t>0.0023,0.9934,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.9888,0.0040,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0004,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.0371,0.9676,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9871,0.1873,0.0001</t>
+  </si>
+  <si>
+    <t>0.0103,0.9543,0.0149,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0069,0.9855,0.0014</t>
+  </si>
+  <si>
+    <t>0.0052,0.0145,0.9869,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9869,0.0045</t>
+  </si>
+  <si>
+    <t>0.0051,0.0004,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9994,0.0005</t>
+  </si>
+  <si>
+    <t>0.0179,0.0362,0.0008,0.9825</t>
+  </si>
+  <si>
+    <t>0.0119,0.9797,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0023,0.9930,0.0070,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9981,0.0020</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9281,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9984,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9945,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9987,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9869,0.0009,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.9535,0.0047,0.0187,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0011,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9574,0.9917,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9526,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0009,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0033,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0028,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9815,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9663,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.5794,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9913,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9723,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9826,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0054,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0009,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0035,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0019,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9866,0.0003,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0306,0.0002,0.9655,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0007,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.9996,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0391,0.9652,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.3965,0.0007,0.5462,0.0023</t>
-  </si>
-  <si>
-    <t>0.6257,0.0001,0.4678,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0302,0.0010,0.9654,0.0004</t>
-  </si>
-  <si>
-    <t>0.0207,0.0000,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0105,0.0000,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.0000,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0819,0.9262,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9157,0.0788,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9535,0.0301,0.0056,0.0006</t>
-  </si>
-  <si>
-    <t>0.9927,0.0007,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.4431,0.6281,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9987,0.0115,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9923,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0018,0.9880,0.0004</t>
-  </si>
-  <si>
-    <t>0.0081,0.0029,0.9824,0.0004</t>
-  </si>
-  <si>
-    <t>0.0567,0.0000,0.8763,0.0008</t>
+    <t>0.0587,0.9448,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.7475,0.0031,0.2118,0.0009</t>
+  </si>
+  <si>
+    <t>0.9638,0.0001,0.0556,0.0001</t>
+  </si>
+  <si>
+    <t>0.5508,0.0016,0.1853,0.0236</t>
+  </si>
+  <si>
+    <t>0.3013,0.0019,0.6000,0.0043</t>
+  </si>
+  <si>
+    <t>0.0008,0.4641,0.0045,0.9570</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9865,0.8271,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9285,0.0912,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7161,0.2990,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9950,0.0014,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.4386,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8317,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0036,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0036,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9331,0.0040,0.0285,0.0022</t>
+  </si>
+  <si>
+    <t>0.0469,0.0001,0.9816,0.0000</t>
+  </si>
+  <si>
+    <t>0.9231,0.0003,0.0696,0.0009</t>
+  </si>
+  <si>
+    <t>0.1352,0.0000,0.0000,0.9743</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.9926,0.4067,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9963,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0040,0.9967,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0002,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.2887,0.0001,0.0032,0.7327</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9983,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0000,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0503,0.5004,0.3061,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9661,0.0062,0.0123,0.0004</t>
+  </si>
+  <si>
+    <t>0.1841,0.4259,0.0715,0.0013</t>
+  </si>
+  <si>
+    <t>0.8383,0.0037,0.1938,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9748,0.0141,0.0048,0.0013</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0098,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8923,0.1714,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9768,0.0233,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9251,0.1115,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9887,0.0051,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8729,0.0152,0.0812,0.0011</t>
   </si>
   <si>
     <t>0.0001,0.0003,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9995,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.7826,0.0001,0.9889</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9967,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.0000,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9597,0.0035,0.0355,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9601,0.0582,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9827,0.9939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.9960,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0672,0.0003,0.9655,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9935,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9854,0.8275,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.2514,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0083,0.9985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0023,0.9994</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0012,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9805,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.8919,0.9138,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9735,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.6813,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
+    <t>0.9872,0.0083,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0118,0.9866,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0890,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0119,0.0054,0.9783,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0011,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.9690,0.0014,0.0161,0.0004</t>
+  </si>
+  <si>
+    <t>0.0179,0.0050,0.9677,0.0002</t>
+  </si>
+  <si>
+    <t>0.0724,0.1226,0.5544,0.0004</t>
+  </si>
+  <si>
+    <t>0.2098,0.0273,0.7052,0.0003</t>
+  </si>
+  <si>
+    <t>0.9503,0.0003,0.0211,0.0031</t>
+  </si>
+  <si>
+    <t>0.6153,0.0050,0.3271,0.0011</t>
+  </si>
+  <si>
+    <t>0.0277,0.9785,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9968,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9163,0.1070,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.5241,0.6086,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0056,0.9932,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9867,0.0010,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.8977,0.0004,0.1235,0.0003</t>
+  </si>
+  <si>
+    <t>0.9274,0.0004,0.0144,0.0102</t>
+  </si>
+  <si>
+    <t>0.9009,0.0155,0.0337,0.0015</t>
+  </si>
+  <si>
+    <t>0.5274,0.0006,0.5245,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9974,0.0007</t>
+  </si>
+  <si>
+    <t>0.0440,0.0040,0.9498,0.0006</t>
+  </si>
+  <si>
+    <t>0.0329,0.0031,0.9596,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0572,0.9688,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0065,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0214,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.9984,0.0006</t>
+  </si>
+  <si>
+    <t>0.0096,0.0122,0.9765,0.0006</t>
+  </si>
+  <si>
+    <t>0.9480,0.0003,0.0327,0.0007</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0432,0.9631,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0006,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0021,0.9922,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0087,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.4314,0.0034,0.5358,0.0012</t>
+  </si>
+  <si>
+    <t>0.9784,0.0003,0.0137,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0005,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0015,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0033,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0023,0.0008,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9969,0.0015,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0099,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0014,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0048,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9903,0.0002,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.0068,0.0001,0.9942,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9985,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4789,0.5866,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9506,0.0012,0.0333,0.0008</t>
-  </si>
-  <si>
-    <t>0.8201,0.0003,0.2688,0.0001</t>
-  </si>
-  <si>
-    <t>0.9420,0.0037,0.0202,0.0015</t>
-  </si>
-  <si>
-    <t>0.9466,0.0013,0.0373,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.4979,0.0016,0.9505</t>
-  </si>
-  <si>
-    <t>0.0005,0.9981,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9820,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.9803,0.0158,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9679,0.0367,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9440,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9650,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4407,0.0021,0.5528,0.0014</t>
-  </si>
-  <si>
-    <t>0.2167,0.0001,0.8897,0.0000</t>
-  </si>
-  <si>
-    <t>0.3199,0.0027,0.7019,0.0014</t>
-  </si>
-  <si>
-    <t>0.5358,0.0003,0.0001,0.6985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9876,0.0923,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0131,0.9843,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.1169,0.9283,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9949,0.0000,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.6821,0.0005,0.0092,0.1932</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.9991,0.0007</t>
-  </si>
-  <si>
-    <t>0.9880,0.0000,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.9923,0.0000,0.0067,0.0002</t>
-  </si>
-  <si>
-    <t>0.0325,0.5529,0.2573,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9926,0.0019,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0798,0.8918,0.0056,0.0016</t>
-  </si>
-  <si>
-    <t>0.1823,0.0571,0.6781,0.0003</t>
-  </si>
-  <si>
-    <t>0.9653,0.0097,0.0101,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0011,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0002,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0021,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8527,0.2169,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9683,0.0303,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0123,0.0015,0.9879,0.0004</t>
-  </si>
-  <si>
-    <t>0.9678,0.0514,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9932,0.0019,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9624,0.0058,0.0173,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9891,0.0025,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0031,0.9909,0.0010</t>
-  </si>
-  <si>
-    <t>0.0007,0.0255,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0032,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.0004,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.0592,0.0087,0.9134,0.0021</t>
-  </si>
-  <si>
-    <t>0.5154,0.0489,0.2997,0.0004</t>
-  </si>
-  <si>
-    <t>0.0654,0.1559,0.4594,0.0001</t>
-  </si>
-  <si>
-    <t>0.6709,0.0119,0.3423,0.0003</t>
-  </si>
-  <si>
-    <t>0.9835,0.0011,0.0026,0.0010</t>
-  </si>
-  <si>
-    <t>0.4071,0.0003,0.6251,0.0007</t>
-  </si>
-  <si>
-    <t>0.3008,0.7939,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9978,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8280,0.2688,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9253,0.1299,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0145,0.9852,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9625,0.0064,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.9384,0.0002,0.0497,0.0010</t>
-  </si>
-  <si>
-    <t>0.9967,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.3171,0.0212,0.6219,0.0049</t>
-  </si>
-  <si>
-    <t>0.7144,0.0005,0.3303,0.0008</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0119,0.0159,0.9714,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0010,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0252,0.9931,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0015,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9776,0.0193,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.9983,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0040,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0045,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0129,0.0153,0.9586,0.0009</t>
-  </si>
-  <si>
-    <t>0.4242,0.0005,0.5830,0.0010</t>
-  </si>
-  <si>
-    <t>0.0024,0.0002,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0016,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.1210,0.9777,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0383,0.0004,0.9745,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0073,0.9922,0.0008</t>
-  </si>
-  <si>
-    <t>0.1206,0.0059,0.8388,0.0014</t>
-  </si>
-  <si>
-    <t>0.8415,0.0002,0.1452,0.0010</t>
-  </si>
-  <si>
-    <t>0.9884,0.0001,0.0104,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0016,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0036,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0022,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0294,0.0173,0.9130,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.0291,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0561,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.0123,0.0088,0.9653,0.0015</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0019,0.9923,0.0036</t>
-  </si>
-  <si>
-    <t>0.0038,0.0014,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0005,0.9939,0.0017</t>
-  </si>
-  <si>
-    <t>0.7686,0.0000,0.0043,0.2087</t>
-  </si>
-  <si>
-    <t>0.0177,0.0007,0.0000,0.9945</t>
-  </si>
-  <si>
-    <t>0.0412,0.0000,0.0001,0.9922</t>
-  </si>
-  <si>
-    <t>0.9940,0.0002,0.0006,0.0009</t>
+    <t>0.0034,0.0056,0.9884,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0085,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3884,0.9946,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0065,0.9909,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0068,0.0002,0.9805,0.0019</t>
+  </si>
+  <si>
+    <t>0.0178,0.0012,0.9761,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.0022,0.9923,0.0031</t>
+  </si>
+  <si>
+    <t>0.9847,0.0000,0.0020,0.0056</t>
+  </si>
+  <si>
+    <t>0.0032,0.0015,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0293,0.0000,0.0000,0.9972</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.8793,0.0001,0.0006,0.1236</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1926,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1954,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1968,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1982,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,10 +2049,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2189,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2203,10 +2203,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2301,10 +2301,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,10 +2497,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2847,10 +2847,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,10 +2903,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2920,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>317</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3228,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>282</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3480,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,10 +3519,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,7 +3536,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>271</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,10 +3757,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3827,10 +3827,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,10 +3855,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3970,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +3984,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,10 +4009,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,7 +4082,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,10 +4121,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4135,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>419</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,7 +4320,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>316</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,10 +4541,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4555,10 +4555,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4569,10 +4569,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,10 +4583,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4656,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,10 +4667,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4737,10 +4737,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,10 +4751,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,7 +4964,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,10 +4975,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>470</v>
+        <v>424</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +5020,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5104,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>270</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5188,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>351</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5328,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5412,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>395</v>
+        <v>493</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:4">

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
   <si>
     <t>Filename</t>
   </si>
@@ -808,697 +808,715 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8825,0.0049,0.0564,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9426,0.0004,0.0015,0.0338</t>
-  </si>
-  <si>
-    <t>0.0285,0.0000,0.0004,0.9906</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9464,0.0052,0.0212,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.8753,0.0012,0.0007,0.0882</t>
+  </si>
+  <si>
+    <t>0.0236,0.0001,0.0003,0.9926</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9521,0.0034,0.0234,0.0005</t>
+  </si>
+  <si>
+    <t>0.1394,0.0004,0.9327,0.0001</t>
+  </si>
+  <si>
+    <t>0.0393,0.0004,0.9771,0.0001</t>
+  </si>
+  <si>
+    <t>0.0101,0.0002,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.9884,0.0002,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9982,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.9948,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9305,0.0008,0.0496,0.0011</t>
+  </si>
+  <si>
+    <t>0.3015,0.0006,0.7744,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0024,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0135,0.0000,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0002,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.8069,0.2402,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.7955,0.0863,0.0579,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9995,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0020,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8806,0.0005,0.1622,0.0002</t>
+  </si>
+  <si>
+    <t>0.0264,0.9741,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.8194,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.9052,0.0561,0.0010</t>
+  </si>
+  <si>
+    <t>0.0033,0.0005,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0084,0.9924,0.0003</t>
+  </si>
+  <si>
+    <t>0.0320,0.0002,0.9630,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.2327,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9597,0.0005,0.9645</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9995,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9344,0.9745,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.9968,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3278,0.0006,0.7747,0.0001</t>
+  </si>
+  <si>
+    <t>0.0162,0.0013,0.9838,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9992,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9776,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9226,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0248,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9432,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0037,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0010,0.9995</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9909,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9966,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9970,0.1617,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.6513,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9846,0.3176,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0046,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9721,0.0013,0.0124,0.0005</t>
-  </si>
-  <si>
-    <t>0.0026,0.0015,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0371,0.0013,0.9764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.0006,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0002,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.9882,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9977,0.0004,0.0011</t>
+    <t>0.9980,0.0020,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9609,0.0002,0.0134,0.0029</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9962,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0629,0.9456,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.8355,0.0022,0.1327,0.0009</t>
+  </si>
+  <si>
+    <t>0.7213,0.0002,0.3210,0.0003</t>
+  </si>
+  <si>
+    <t>0.2391,0.3534,0.0495,0.0014</t>
+  </si>
+  <si>
+    <t>0.6013,0.0068,0.2634,0.0040</t>
+  </si>
+  <si>
+    <t>0.0001,0.8621,0.0003,0.9743</t>
+  </si>
+  <si>
+    <t>0.0007,0.9979,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8506,0.0005,0.0952,0.0034</t>
-  </si>
-  <si>
-    <t>0.2055,0.0006,0.7455,0.0019</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0002,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0587,0.0001,0.9761,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.0000,0.9918,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.1085,0.9008,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0766,0.1193,0.6857,0.0007</t>
-  </si>
-  <si>
-    <t>0.0017,0.0006,0.9987,0.0009</t>
-  </si>
-  <si>
-    <t>0.0023,0.9934,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.9888,0.0040,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9924,0.0004,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.0371,0.9676,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9871,0.1873,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.9543,0.0149,0.0007</t>
-  </si>
-  <si>
-    <t>0.0056,0.0069,0.9855,0.0014</t>
-  </si>
-  <si>
-    <t>0.0052,0.0145,0.9869,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0007,0.9869,0.0045</t>
-  </si>
-  <si>
-    <t>0.0051,0.0004,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0179,0.0362,0.0008,0.9825</t>
-  </si>
-  <si>
-    <t>0.0119,0.9797,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0023,0.9930,0.0070,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9981,0.0020</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9281,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9987,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9869,0.0009,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.9535,0.0047,0.0187,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0011,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9574,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.9526,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9929,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0009,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0033,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0028,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9815,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9663,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.5794,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9913,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9723,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9826,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0054,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0035,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0019,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0021,0.0002,0.0001</t>
+    <t>0.0000,0.9891,0.9755,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7062,0.3642,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9810,0.0114,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0005,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0003,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.0306,0.0002,0.9655,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.9982,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0587,0.9448,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.7475,0.0031,0.2118,0.0009</t>
-  </si>
-  <si>
-    <t>0.9638,0.0001,0.0556,0.0001</t>
-  </si>
-  <si>
-    <t>0.5508,0.0016,0.1853,0.0236</t>
-  </si>
-  <si>
-    <t>0.3013,0.0019,0.6000,0.0043</t>
-  </si>
-  <si>
-    <t>0.0008,0.4641,0.0045,0.9570</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9865,0.8271,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9285,0.0912,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.7161,0.2990,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9950,0.0014,0.0010,0.0005</t>
+    <t>0.9996,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9057,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7835,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4034,0.0015,0.5313,0.0024</t>
+  </si>
+  <si>
+    <t>0.2172,0.0000,0.9047,0.0000</t>
+  </si>
+  <si>
+    <t>0.9681,0.0004,0.0219,0.0008</t>
+  </si>
+  <si>
+    <t>0.0894,0.0001,0.0006,0.9685</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0006,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.9919,0.3229,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.9935,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.3114,0.8032,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.8225,0.0001,0.0008,0.1939</t>
+  </si>
+  <si>
+    <t>0.0006,0.0009,0.9985,0.0018</t>
+  </si>
+  <si>
+    <t>0.9902,0.0000,0.0053,0.0007</t>
+  </si>
+  <si>
+    <t>0.9836,0.0001,0.0120,0.0005</t>
+  </si>
+  <si>
+    <t>0.5424,0.2259,0.0554,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9776,0.0051,0.0056,0.0006</t>
+  </si>
+  <si>
+    <t>0.4807,0.0793,0.0764,0.0030</t>
+  </si>
+  <si>
+    <t>0.9278,0.0060,0.0396,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0006,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.4386,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8317,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0036,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0036,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9331,0.0040,0.0285,0.0022</t>
-  </si>
-  <si>
-    <t>0.0469,0.0001,0.9816,0.0000</t>
-  </si>
-  <si>
-    <t>0.9231,0.0003,0.0696,0.0009</t>
-  </si>
-  <si>
-    <t>0.1352,0.0000,0.0000,0.9743</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9926,0.4067,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9963,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.0040,0.9967,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.2887,0.0001,0.0032,0.7327</t>
-  </si>
-  <si>
-    <t>0.0012,0.0010,0.9983,0.0007</t>
-  </si>
-  <si>
-    <t>0.9957,0.0000,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0503,0.5004,0.3061,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9661,0.0062,0.0123,0.0004</t>
-  </si>
-  <si>
-    <t>0.1841,0.4259,0.0715,0.0013</t>
-  </si>
-  <si>
-    <t>0.8383,0.0037,0.1938,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9748,0.0141,0.0048,0.0013</t>
+    <t>0.9904,0.0076,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.8883,0.1585,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9297,0.0949,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0176,0.0034,0.9797,0.0012</t>
+  </si>
+  <si>
+    <t>0.9927,0.0062,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0013,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9672,0.0092,0.0116,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9865,0.0046,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0036,0.9942,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.2114,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1228,0.0004,0.9008,0.0003</t>
+  </si>
+  <si>
+    <t>0.2968,0.0072,0.7109,0.0010</t>
+  </si>
+  <si>
+    <t>0.0110,0.0050,0.9849,0.0002</t>
+  </si>
+  <si>
+    <t>0.0731,0.0202,0.7730,0.0003</t>
+  </si>
+  <si>
+    <t>0.0088,0.8616,0.1148,0.0003</t>
+  </si>
+  <si>
+    <t>0.9225,0.0071,0.0534,0.0005</t>
+  </si>
+  <si>
+    <t>0.9765,0.0010,0.0073,0.0011</t>
+  </si>
+  <si>
+    <t>0.0080,0.0004,0.9916,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9954,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8023,0.2813,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.1299,0.8989,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0440,0.9657,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9950,0.0012,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8580,0.0004,0.1447,0.0009</t>
+  </si>
+  <si>
+    <t>0.9855,0.0003,0.0046,0.0006</t>
+  </si>
+  <si>
+    <t>0.4468,0.0130,0.4204,0.0048</t>
+  </si>
+  <si>
+    <t>0.2739,0.0004,0.7503,0.0010</t>
+  </si>
+  <si>
+    <t>0.0110,0.0006,0.9903,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.0058,0.9868,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.0146,0.9906,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.0004,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0451,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0126,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0049,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.1933,0.0201,0.6288,0.0015</t>
+  </si>
+  <si>
+    <t>0.1681,0.0005,0.7654,0.0086</t>
+  </si>
+  <si>
+    <t>0.5753,0.0002,0.7003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0050,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.2355,0.9607,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0080,0.0002,0.9886,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0173,0.9955,0.0007</t>
+  </si>
+  <si>
+    <t>0.9479,0.0010,0.0341,0.0010</t>
+  </si>
+  <si>
+    <t>0.9607,0.0004,0.0281,0.0007</t>
+  </si>
+  <si>
+    <t>0.9818,0.0008,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0030,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0049,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0026,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9868,0.0098,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8923,0.1714,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9768,0.0233,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0008,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.9251,0.1115,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0051,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8729,0.0152,0.0812,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0083,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0118,0.9866,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0890,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0119,0.0054,0.9783,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.0011,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.9690,0.0014,0.0161,0.0004</t>
-  </si>
-  <si>
-    <t>0.0179,0.0050,0.9677,0.0002</t>
-  </si>
-  <si>
-    <t>0.0724,0.1226,0.5544,0.0004</t>
-  </si>
-  <si>
-    <t>0.2098,0.0273,0.7052,0.0003</t>
-  </si>
-  <si>
-    <t>0.9503,0.0003,0.0211,0.0031</t>
-  </si>
-  <si>
-    <t>0.6153,0.0050,0.3271,0.0011</t>
-  </si>
-  <si>
-    <t>0.0277,0.9785,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.9968,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9163,0.1070,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.5241,0.6086,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9932,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9867,0.0010,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.8977,0.0004,0.1235,0.0003</t>
-  </si>
-  <si>
-    <t>0.9274,0.0004,0.0144,0.0102</t>
-  </si>
-  <si>
-    <t>0.9009,0.0155,0.0337,0.0015</t>
-  </si>
-  <si>
-    <t>0.5274,0.0006,0.5245,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9974,0.0007</t>
-  </si>
-  <si>
-    <t>0.0440,0.0040,0.9498,0.0006</t>
-  </si>
-  <si>
-    <t>0.0329,0.0031,0.9596,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0572,0.9688,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9920,0.0065,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9784,0.0214,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9984,0.0006</t>
-  </si>
-  <si>
-    <t>0.0096,0.0122,0.9765,0.0006</t>
-  </si>
-  <si>
-    <t>0.9480,0.0003,0.0327,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.0432,0.9631,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0006,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.0021,0.9922,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0087,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.4314,0.0034,0.5358,0.0012</t>
-  </si>
-  <si>
-    <t>0.9784,0.0003,0.0137,0.0004</t>
-  </si>
-  <si>
-    <t>0.9927,0.0005,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0015,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0033,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0023,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0056,0.9884,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0085,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3884,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0065,0.9909,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.0002,0.9805,0.0019</t>
-  </si>
-  <si>
-    <t>0.0178,0.0012,0.9761,0.0007</t>
-  </si>
-  <si>
-    <t>0.0017,0.0022,0.9923,0.0031</t>
-  </si>
-  <si>
-    <t>0.9847,0.0000,0.0020,0.0056</t>
-  </si>
-  <si>
-    <t>0.0032,0.0015,0.0001,0.9984</t>
-  </si>
-  <si>
-    <t>0.0293,0.0000,0.0000,0.9972</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.8793,0.0001,0.0006,0.1236</t>
+    <t>0.0002,0.0028,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0028,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0094,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0050,0.9931,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0359,0.0003,0.9355,0.0045</t>
+  </si>
+  <si>
+    <t>0.0595,0.0007,0.9442,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.9960,0.0017</t>
+  </si>
+  <si>
+    <t>0.9619,0.0000,0.0043,0.0146</t>
+  </si>
+  <si>
+    <t>0.0015,0.0018,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.0110,0.0000,0.0001,0.9972</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0001,0.0001,0.0009</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1916,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1926,7 +1944,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1954,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1968,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1982,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2052,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2084,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,7 +2098,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2126,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2168,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,7 +2210,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,7 +2224,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2266,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2287,10 +2305,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2301,10 +2319,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2378,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2392,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2385,10 +2403,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,7 +2420,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,10 +2515,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2546,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2560,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2574,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2588,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2602,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2630,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2658,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2672,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2700,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2742,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2784,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2826,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2840,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2833,10 +2851,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2847,10 +2865,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2882,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2910,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,10 +2921,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2920,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3036,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,10 +3061,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3078,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,10 +3103,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3116,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3344,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3358,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3498,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,10 +3523,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,10 +3537,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3533,10 +3551,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3596,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3610,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,7 +3652,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,10 +3775,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3792,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3806,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3827,10 +3845,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3862,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3858,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3904,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3918,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3932,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3928,7 +3946,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3956,7 +3974,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3988,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +4002,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +4016,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,10 +4027,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4058,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4079,10 +4097,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,10 +4139,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>359</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>272</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,7 +4310,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4324,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,7 +4338,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4366,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4394,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,10 +4559,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4558,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4569,10 +4587,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,10 +4601,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4629,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4646,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4656,7 +4674,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,7 +4688,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4702,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4716,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4737,10 +4755,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,7 +4772,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4814,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4842,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,7 +4982,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,10 +4993,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4989,10 +5007,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>424</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +5038,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5080,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,10 +5119,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,7 +5136,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>475</v>
+        <v>359</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5304,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5388,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5416,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5412,7 +5430,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5440,7 +5458,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
